--- a/artfynd/A 56916-2025 artfynd.xlsx
+++ b/artfynd/A 56916-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,324 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130300257</v>
+      </c>
+      <c r="B3" t="n">
+        <v>75119</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>96</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rödprick</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Arthonia helvola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Nyl.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skäggsta, Skäggsta, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>630306</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6930285</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tynderö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130300272</v>
+      </c>
+      <c r="B4" t="n">
+        <v>75119</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>96</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rödprick</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Arthonia helvola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skäggsta, Skäggsta, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>630312</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6930292</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tynderö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130299747</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91952</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skäggsta, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>630343</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6930237</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tynderö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56916-2025 artfynd.xlsx
+++ b/artfynd/A 56916-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>130300257</v>
       </c>
       <c r="B3" t="n">
-        <v>75119</v>
+        <v>75122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>130300272</v>
       </c>
       <c r="B4" t="n">
-        <v>75119</v>
+        <v>75122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>130299747</v>
       </c>
       <c r="B5" t="n">
-        <v>91952</v>
+        <v>91955</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56916-2025 artfynd.xlsx
+++ b/artfynd/A 56916-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>130300257</v>
       </c>
       <c r="B3" t="n">
-        <v>75122</v>
+        <v>75148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>130300272</v>
       </c>
       <c r="B4" t="n">
-        <v>75122</v>
+        <v>75148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>130299747</v>
       </c>
       <c r="B5" t="n">
-        <v>91955</v>
+        <v>91981</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56916-2025 artfynd.xlsx
+++ b/artfynd/A 56916-2025 artfynd.xlsx
@@ -1004,7 +1004,7 @@
         <v>130299747</v>
       </c>
       <c r="B5" t="n">
-        <v>91981</v>
+        <v>91982</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56916-2025 artfynd.xlsx
+++ b/artfynd/A 56916-2025 artfynd.xlsx
@@ -1004,7 +1004,7 @@
         <v>130299747</v>
       </c>
       <c r="B5" t="n">
-        <v>91982</v>
+        <v>91983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56916-2025 artfynd.xlsx
+++ b/artfynd/A 56916-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>130300257</v>
       </c>
       <c r="B3" t="n">
-        <v>75148</v>
+        <v>75150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>130300272</v>
       </c>
       <c r="B4" t="n">
-        <v>75148</v>
+        <v>75150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>130299747</v>
       </c>
       <c r="B5" t="n">
-        <v>91983</v>
+        <v>91985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56916-2025 artfynd.xlsx
+++ b/artfynd/A 56916-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>130300257</v>
       </c>
       <c r="B3" t="n">
-        <v>75150</v>
+        <v>75158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>130300272</v>
       </c>
       <c r="B4" t="n">
-        <v>75150</v>
+        <v>75158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>130299747</v>
       </c>
       <c r="B5" t="n">
-        <v>91985</v>
+        <v>91998</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56916-2025 artfynd.xlsx
+++ b/artfynd/A 56916-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>130300257</v>
       </c>
       <c r="B3" t="n">
-        <v>75158</v>
+        <v>75159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>130300272</v>
       </c>
       <c r="B4" t="n">
-        <v>75158</v>
+        <v>75159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>130299747</v>
       </c>
       <c r="B5" t="n">
-        <v>91998</v>
+        <v>91999</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56916-2025 artfynd.xlsx
+++ b/artfynd/A 56916-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>130300257</v>
       </c>
       <c r="B3" t="n">
-        <v>75159</v>
+        <v>75160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>130300272</v>
       </c>
       <c r="B4" t="n">
-        <v>75159</v>
+        <v>75160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>130299747</v>
       </c>
       <c r="B5" t="n">
-        <v>91999</v>
+        <v>92000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56916-2025 artfynd.xlsx
+++ b/artfynd/A 56916-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123601979</v>
+        <v>89428083</v>
       </c>
       <c r="B2" t="n">
-        <v>57519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skäggsta, Mpd</t>
+          <t>Fågelsångens NR, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630347</v>
+        <v>630329</v>
       </c>
       <c r="R2" t="n">
-        <v>6930247</v>
+        <v>6930354</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,27 +738,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Tynderö</t>
+          <t>Hässjö</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2020-12-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2020-12-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130300257</v>
+        <v>130300055</v>
       </c>
       <c r="B3" t="n">
-        <v>75160</v>
+        <v>75261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,19 +805,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skäggsta, Skäggsta, Mpd</t>
+          <t>Fågelsången, Fågelsången, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>630306</v>
+        <v>630277</v>
       </c>
       <c r="R3" t="n">
-        <v>6930285</v>
+        <v>6930279</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +855,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130300272</v>
+        <v>130300257</v>
       </c>
       <c r="B4" t="n">
-        <v>75160</v>
+        <v>75261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,13 +911,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630312</v>
+        <v>630306</v>
       </c>
       <c r="R4" t="n">
-        <v>6930292</v>
+        <v>6930285</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,32 +974,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130299747</v>
+        <v>130300272</v>
       </c>
       <c r="B5" t="n">
-        <v>92000</v>
+        <v>75261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1106</v>
+        <v>96</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Rödprick</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Arthonia helvola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Nyl.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,17 +1008,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skäggsta, Mpd</t>
+          <t>Skäggsta, Skäggsta, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630343</v>
+        <v>630312</v>
       </c>
       <c r="R5" t="n">
-        <v>6930237</v>
+        <v>6930292</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,21 +1060,6 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1114,6 +1072,564 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130300562</v>
+      </c>
+      <c r="B6" t="n">
+        <v>75261</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>96</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rödprick</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Arthonia helvola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fågelsångens NR, Fågelsångens NR, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>630327</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6930332</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tynderö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130299747</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92134</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skäggsta, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>630343</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6930237</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tynderö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123601979</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57966</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skäggsta, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>630347</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6930247</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tynderö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>91790706</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skäggsta, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>630395</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6930264</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tynderö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130300177</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skäggsta, Skäggsta, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>630290</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6930282</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tynderö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56916-2025 artfynd.xlsx
+++ b/artfynd/A 56916-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89428083</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300055</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300257</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300272</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300562</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1285,6 +1315,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130299747</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123601979</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91790706</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,8 +1675,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300177</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>